--- a/public/inputs/y05-science - input.xlsx
+++ b/public/inputs/y05-science - input.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -823,6 +823,240 @@
       </c>
       <c r="C31" t="inlineStr"/>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Term 1 Revision</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Term 1 Assessment</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Term 1 Animal Theory</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Term 1 Animal and Plant Practicals</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Term 1 Plant Theory</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Term 1 School Activities</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Term 2 Revision</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Term 2 Assessment</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Term 2 Animal Theory</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Term 2 Animal and Plant Practicals</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Term 2 Plant Theory</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Term 2 School Activities</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Term 3 Revision</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Term 3 Assessment</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Term 3 Animal Theory</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Term 3 Animal and Plant Practicals</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Term 3 Plant Theory</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Term 3 School Activities</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
